--- a/tabulacao_conteudo_final.xlsx
+++ b/tabulacao_conteudo_final.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -369,381 +369,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10PlayTV</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AnthymTV</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B3">
-        <v>21</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRASIL</t>
+          <t>Great Britain</t>
         </is>
       </c>
       <c r="B4">
-        <v>38</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BumbleBeeTV</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="B5">
-        <v>40</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cineverse</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DistroTV</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FreeMoviesPlus</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FreeTV</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GalxyTV</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GitHubTV</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>14538</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HerogoTV</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Igocast</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Infantis em inglês</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KlowdTV</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LGTV</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LocalNowTV</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>OttTV</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PBSTV</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PlexTV</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PlutoTV</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>2268</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PrimeTV</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>1765</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RakutenTV</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>RewardedTV</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Roku</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RokuTV</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>SamsungTVPlus</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>SportsTV</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>StirrTV</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TabloTV</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TCLTV</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TubiTV</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>VeelyTV</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>VidaaTV</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>VizioTV</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>WebTV</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>XiaomiTV</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>XumoTV</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ZeasnTV</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>40</v>
+        <v>2940</v>
       </c>
     </row>
   </sheetData>

--- a/tabulacao_conteudo_final.xlsx
+++ b/tabulacao_conteudo_final.xlsx
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>5127</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="3">
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>335</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6">

--- a/tabulacao_conteudo_final.xlsx
+++ b/tabulacao_conteudo_final.xlsx
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15">

--- a/tabulacao_conteudo_final.xlsx
+++ b/tabulacao_conteudo_final.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>183</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1363</v>
+        <v>920</v>
       </c>
     </row>
     <row r="4">
@@ -393,67 +393,97 @@
         </is>
       </c>
       <c r="B4">
-        <v>266</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Great Britain</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B5">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Great Britain</t>
         </is>
       </c>
       <c r="B6">
-        <v>615</v>
+        <v>790</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NBA</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B8">
-        <v>54</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B9">
-        <v>333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Omitir</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B10">
-        <v>3693</v>
+      <c r="B13">
+        <v>6756</v>
       </c>
     </row>
   </sheetData>

--- a/tabulacao_conteudo_final.xlsx
+++ b/tabulacao_conteudo_final.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>154</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>459</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="4">
@@ -393,57 +393,107 @@
         </is>
       </c>
       <c r="B4">
-        <v>357</v>
+        <v>822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Great Britain</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B5">
-        <v>168</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Great Britain</t>
         </is>
       </c>
       <c r="B6">
-        <v>287</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="B7">
-        <v>352</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Omitir</t>
+          <t>NBA</t>
         </is>
       </c>
       <c r="B8">
-        <v>3862</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NFL</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Omitir</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B9">
-        <v>332</v>
+      <c r="B14">
+        <v>8617</v>
       </c>
     </row>
   </sheetData>
